--- a/temp/definition of rings.xlsx
+++ b/temp/definition of rings.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="47">
   <si>
     <t>IDEntranceForward</t>
   </si>
@@ -500,8 +500,8 @@
   <dimension ref="A2:AC17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="7" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5703125" style="1" customWidth="1"/>
     <col min="3" max="3" width="11.28515625" style="1" customWidth="1"/>
     <col min="4" max="4" width="19.7109375" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.28515625" style="1" customWidth="1"/>
@@ -509,16 +509,15 @@
     <col min="7" max="7" width="11.140625" style="1" customWidth="1"/>
     <col min="8" max="8" width="19.42578125" style="1" customWidth="1"/>
     <col min="9" max="10" width="9.140625" style="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.42578125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="15" style="1" customWidth="1"/>
+    <col min="12" max="12" width="11.85546875" style="1" customWidth="1"/>
     <col min="13" max="13" width="11.28515625" style="1" customWidth="1"/>
     <col min="14" max="16" width="9.140625" style="1"/>
-    <col min="17" max="17" width="7.5703125" style="1" customWidth="1"/>
-    <col min="18" max="18" width="7.28515625" style="1" customWidth="1"/>
+    <col min="17" max="18" width="9" style="1" customWidth="1"/>
     <col min="19" max="19" width="4.140625" style="1" customWidth="1"/>
     <col min="20" max="20" width="5.28515625" style="1" customWidth="1"/>
     <col min="21" max="21" width="7.5703125" style="1" customWidth="1"/>
-    <col min="22" max="22" width="6.42578125" style="1" customWidth="1"/>
+    <col min="22" max="22" width="7" style="1" customWidth="1"/>
     <col min="23" max="23" width="6" style="1" customWidth="1"/>
     <col min="24" max="24" width="6.28515625" style="1" customWidth="1"/>
     <col min="25" max="25" width="6" style="1" customWidth="1"/>
@@ -656,9 +655,6 @@
       <c r="N4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="P4" s="1" t="s">
-        <v>18</v>
-      </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">

--- a/temp/definition of rings.xlsx
+++ b/temp/definition of rings.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="56">
   <si>
     <t>IDEntranceForward</t>
   </si>
@@ -155,6 +155,33 @@
   </si>
   <si>
     <t>6</t>
+  </si>
+  <si>
+    <t>читать значения по IDFork, чтобы не прочитать мусор в пустых ячейках</t>
+  </si>
+  <si>
+    <t>IDForwardLink</t>
+  </si>
+  <si>
+    <t>IDBackLink</t>
+  </si>
+  <si>
+    <t>IDForwardStep</t>
+  </si>
+  <si>
+    <t>IDBackStep</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>10</t>
   </si>
 </sst>
 </file>
@@ -497,37 +524,37 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:AC17"/>
+  <dimension ref="A2:AJ30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" style="1" customWidth="1"/>
     <col min="2" max="2" width="12.5703125" style="1" customWidth="1"/>
     <col min="3" max="3" width="11.28515625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="19.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11.28515625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="15.140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.140625" style="1" customWidth="1"/>
+    <col min="5" max="6" width="11.28515625" style="1" customWidth="1"/>
     <col min="7" max="7" width="11.140625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="19.42578125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" style="1" customWidth="1"/>
     <col min="9" max="10" width="9.140625" style="1"/>
-    <col min="11" max="11" width="15" style="1" customWidth="1"/>
-    <col min="12" max="12" width="11.85546875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="11.28515625" style="1" customWidth="1"/>
-    <col min="14" max="16" width="9.140625" style="1"/>
-    <col min="17" max="18" width="9" style="1" customWidth="1"/>
-    <col min="19" max="19" width="4.140625" style="1" customWidth="1"/>
-    <col min="20" max="20" width="5.28515625" style="1" customWidth="1"/>
-    <col min="21" max="21" width="7.5703125" style="1" customWidth="1"/>
-    <col min="22" max="22" width="7" style="1" customWidth="1"/>
-    <col min="23" max="23" width="6" style="1" customWidth="1"/>
-    <col min="24" max="24" width="6.28515625" style="1" customWidth="1"/>
-    <col min="25" max="25" width="6" style="1" customWidth="1"/>
-    <col min="26" max="26" width="6.5703125" style="1" customWidth="1"/>
-    <col min="27" max="27" width="6.140625" style="1" customWidth="1"/>
-    <col min="28" max="28" width="6.7109375" style="1" customWidth="1"/>
-    <col min="29" max="29" width="9.140625" style="1"/>
+    <col min="11" max="12" width="15" style="1" customWidth="1"/>
+    <col min="13" max="14" width="11.85546875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="9.140625" style="1"/>
+    <col min="16" max="17" width="11.28515625" style="1" customWidth="1"/>
+    <col min="18" max="20" width="9.140625" style="1"/>
+    <col min="21" max="22" width="9" style="1" customWidth="1"/>
+    <col min="23" max="23" width="14.7109375" style="1" customWidth="1"/>
+    <col min="24" max="24" width="7.28515625" style="1" customWidth="1"/>
+    <col min="25" max="26" width="7" style="1" customWidth="1"/>
+    <col min="27" max="27" width="6" style="1" customWidth="1"/>
+    <col min="28" max="28" width="6.28515625" style="1" customWidth="1"/>
+    <col min="29" max="29" width="6" style="1" customWidth="1"/>
+    <col min="30" max="30" width="6.5703125" style="1" customWidth="1"/>
+    <col min="31" max="31" width="6.140625" style="1" customWidth="1"/>
+    <col min="32" max="32" width="11.28515625" style="1" customWidth="1"/>
+    <col min="33" max="33" width="10.28515625" style="1" customWidth="1"/>
+    <col min="34" max="34" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -559,37 +586,62 @@
         <v>7</v>
       </c>
       <c r="L2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="M2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="O2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="P2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="R2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="T2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="U2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="V2" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="X2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="AD2" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="T2" s="1" t="s">
+      <c r="AE2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="U2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="V2" s="1" t="s">
+      <c r="AF2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="AG2" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="AI2" s="1"/>
+    </row>
+    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>18</v>
       </c>
@@ -609,37 +661,62 @@
         <v>18</v>
       </c>
       <c r="L3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="M3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="M3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="N3" s="1" t="s">
+      <c r="O3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="R3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="P3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="S3" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="T3" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="U3" s="1" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="V3" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="W3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="X3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AD3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AE3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AF3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AG3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AI3" s="1"/>
+    </row>
+    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
       <c r="J4" s="1" t="s">
         <v>18</v>
       </c>
@@ -647,16 +724,25 @@
         <v>18</v>
       </c>
       <c r="L4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="M4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="N4" s="1" t="s">
+      <c r="O4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R4" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
@@ -688,37 +774,46 @@
         <v>7</v>
       </c>
       <c r="L6" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q6" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="R6" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="T6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="U6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="V6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="W6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="X6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="M6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="N6" s="1" t="s">
+      <c r="Z6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="P6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="R6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="S6" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="T6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="U6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="V6" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>18</v>
       </c>
@@ -738,31 +833,40 @@
         <v>18</v>
       </c>
       <c r="L7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="M7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="M7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="N7" s="1" t="s">
+      <c r="O7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="R7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="P7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="R7" s="1" t="s">
+      <c r="T7" s="1" t="s">
         <v>18</v>
       </c>
       <c r="U7" s="1" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="V7" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="Y7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z7" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>19</v>
       </c>
@@ -794,34 +898,43 @@
         <v>18</v>
       </c>
       <c r="L8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="M8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="N8" s="1" t="s">
+      <c r="O8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R8" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q8" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="R8" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="U8" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="V8" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="W8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="X8" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="Y8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB8" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>28</v>
       </c>
@@ -853,40 +966,49 @@
         <v>19</v>
       </c>
       <c r="L9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="M9" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="M9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="N9" s="1" t="s">
+      <c r="O9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="R9" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="Q9" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="R9" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="U9" s="1" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="V9" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="W9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="X9" s="1" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="Y9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AC9" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="Z9" s="1" t="s">
+      <c r="AD9" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>28</v>
       </c>
@@ -918,40 +1040,49 @@
         <v>19</v>
       </c>
       <c r="L10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="M10" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="M10" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="N10" s="1" t="s">
+      <c r="O10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="R10" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q10" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="R10" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="U10" s="1" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="V10" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="W10" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="X10" s="1" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="Y10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AC10" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="Z10" s="1" t="s">
+      <c r="AD10" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>31</v>
       </c>
@@ -971,43 +1102,52 @@
         <v>28</v>
       </c>
       <c r="L11" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="M11" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="M11" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="N11" s="1" t="s">
+      <c r="O11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q11" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="R11" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="P11" s="1" t="s">
+      <c r="T11" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="Q11" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="R11" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="U11" s="1" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="V11" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="W11" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="X11" s="1" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="Y11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AC11" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="Z11" s="1" t="s">
+      <c r="AD11" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>31</v>
       </c>
@@ -1027,43 +1167,52 @@
         <v>31</v>
       </c>
       <c r="L12" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="M12" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="M12" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="N12" s="1" t="s">
+      <c r="O12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q12" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="R12" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="P12" s="1" t="s">
+      <c r="T12" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="Q12" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="R12" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="U12" s="1" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="V12" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="W12" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="X12" s="1" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="Y12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB12" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AC12" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="Z12" s="1" t="s">
+      <c r="AD12" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.25">
       <c r="J13" s="1" t="s">
         <v>19</v>
       </c>
@@ -1071,52 +1220,61 @@
         <v>31</v>
       </c>
       <c r="L13" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="M13" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="M13" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="N13" s="1" t="s">
+      <c r="O13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="P13" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q13" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="R13" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="P13" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q13" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="R13" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="S13" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="T13" s="1" t="s">
         <v>19</v>
       </c>
       <c r="U13" s="1" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="V13" s="1" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="W13" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="X13" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="Y13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB13" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AC13" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="Z13" s="1" t="s">
+      <c r="AD13" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AA13" s="1" t="s">
+      <c r="AE13" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:35" x14ac:dyDescent="0.25">
       <c r="J14" s="1" t="s">
         <v>19</v>
       </c>
@@ -1124,46 +1282,55 @@
         <v>31</v>
       </c>
       <c r="L14" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="M14" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="M14" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="N14" s="1" t="s">
+      <c r="O14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="P14" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q14" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="R14" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="P14" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q14" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="R14" s="1" t="s">
+      <c r="T14" s="1" t="s">
         <v>28</v>
       </c>
       <c r="U14" s="1" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="V14" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="W14" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="X14" s="1" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="Y14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA14" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AC14" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="Z14" s="1" t="s">
+      <c r="AD14" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AA14" s="1" t="s">
+      <c r="AE14" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.25">
       <c r="J15" s="1" t="s">
         <v>19</v>
       </c>
@@ -1171,40 +1338,43 @@
         <v>31</v>
       </c>
       <c r="L15" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="M15" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="P15" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q15" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="R15" s="1" t="s">
-        <v>28</v>
+      <c r="T15" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="U15" s="1" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="V15" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="W15" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="X15" s="1" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="Y15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z15" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB15" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AC15" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="Z15" s="1" t="s">
+      <c r="AD15" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AA15" s="1" t="s">
+      <c r="AE15" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.25">
       <c r="J16" s="1" t="s">
         <v>19</v>
       </c>
@@ -1212,40 +1382,43 @@
         <v>31</v>
       </c>
       <c r="L16" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="M16" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="P16" s="1" t="s">
+      <c r="T16" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="Q16" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="R16" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="U16" s="1" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="V16" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="W16" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="X16" s="1" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="Y16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AC16" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="Z16" s="1" t="s">
+      <c r="AD16" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AA16" s="1" t="s">
+      <c r="AE16" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="10:36" x14ac:dyDescent="0.25">
       <c r="J17" s="1" t="s">
         <v>19</v>
       </c>
@@ -1253,7 +1426,382 @@
         <v>31</v>
       </c>
       <c r="L17" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="M17" s="1" t="s">
         <v>42</v>
+      </c>
+    </row>
+    <row r="18" spans="10:36" x14ac:dyDescent="0.25">
+      <c r="Y18" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="20" spans="10:36" x14ac:dyDescent="0.25">
+      <c r="S20" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="T20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="U20" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="V20" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="W20" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="X20" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC20" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE20" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF20" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG20" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="AH20" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="10:36" x14ac:dyDescent="0.25">
+      <c r="S21" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T21" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="W21" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="X21" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC21" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AD21" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AG21" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AH21" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="10:36" x14ac:dyDescent="0.25">
+      <c r="T22" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="W22" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="X22" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y22" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD22" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AG22" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AH22" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AI22" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="10:36" x14ac:dyDescent="0.25">
+      <c r="T23" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="W23" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="X23" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y23" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z23" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AD23" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AG23" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AH23" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AI23" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AJ23" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="24" spans="10:36" x14ac:dyDescent="0.25">
+      <c r="T24" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="X24" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y24" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z24" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AD24" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AH24" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AI24" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AJ24" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="25" spans="10:36" x14ac:dyDescent="0.25">
+      <c r="S25" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="T25" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="X25" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y25" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z25" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC25" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AD25" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AH25" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AI25" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AJ25" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="26" spans="10:36" x14ac:dyDescent="0.25">
+      <c r="S26" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="T26" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="X26" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y26" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z26" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC26" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD26" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AH26" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AI26" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AJ26" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="27" spans="10:36" x14ac:dyDescent="0.25">
+      <c r="S27" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="T27" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="U27" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="V27" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="W27" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="X27" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y27" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z27" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA27" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC27" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AD27" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE27" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AF27" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AH27" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AI27" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AJ27" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="10:36" x14ac:dyDescent="0.25">
+      <c r="S28" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="T28" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="X28" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y28" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z28" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA28" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC28" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD28" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AH28" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AI28" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AJ28" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29" spans="10:36" x14ac:dyDescent="0.25">
+      <c r="S29" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="T29" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="X29" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y29" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z29" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA29" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC29" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD29" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AH29" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AI29" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AJ29" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="30" spans="10:36" x14ac:dyDescent="0.25">
+      <c r="S30" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="T30" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="X30" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y30" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z30" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA30" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC30" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD30" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AH30" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AI30" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AJ30" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/temp/definition of rings.xlsx
+++ b/temp/definition of rings.xlsx
@@ -160,20 +160,27 @@
     <t>если нет схождения в кольцо - текущую строку удалить</t>
   </si>
   <si>
-    <t>в конце удалить с конца повторяющиеся линки</t>
-  </si>
-  <si>
     <t>если нет схождения в кольцо - новые строки удалить</t>
+  </si>
+  <si>
+    <t>в конце обхода удалить с конца повторяющиеся линки</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B0F0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -199,9 +206,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -786,12 +794,12 @@
     </row>
     <row r="17" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B17" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B18" s="2" t="s">
         <v>48</v>
-      </c>
-    </row>
-    <row r="18" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B18" s="1" t="s">
-        <v>49</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>0</v>
@@ -1144,7 +1152,7 @@
       </c>
     </row>
     <row r="31" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="I31" s="1" t="s">
+      <c r="I31" s="2" t="s">
         <v>47</v>
       </c>
     </row>
